--- a/inputs/targets.xlsx
+++ b/inputs/targets.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8739640-E4A7-4A9B-8826-0F0E190E9D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80DD9F9-E07A-4B29-B444-BA0FBB34F5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31065" yWindow="2115" windowWidth="14685" windowHeight="11835" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
+    <workbookView xWindow="29775" yWindow="1725" windowWidth="10845" windowHeight="7005" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,7 +23,9 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
@@ -38,9 +40,6 @@
     <t>Target_Idx</t>
   </si>
   <si>
-    <t>Target_Range_km</t>
-  </si>
-  <si>
     <t>Target_Vel_m</t>
   </si>
   <si>
@@ -48,6 +47,9 @@
   </si>
   <si>
     <t>Target_RCS</t>
+  </si>
+  <si>
+    <t>Target_Range_m</t>
   </si>
 </sst>
 </file>
@@ -401,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8C7F47-36BB-473A-8C1D-3059C9614FE4}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -415,30 +417,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>500</v>
+      <c r="B2" s="1">
+        <v>600000</v>
       </c>
       <c r="C2" s="1">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2">
         <v>1</v>
@@ -448,153 +450,34 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>601</v>
+      <c r="B3" s="1">
+        <v>500000</v>
       </c>
       <c r="C3" s="1">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
         <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>702</v>
+      <c r="B4" s="1">
+        <v>300000</v>
       </c>
       <c r="C4" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>803</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>904</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>405</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2000</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>306</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D8">
-        <v>100</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>207</v>
-      </c>
-      <c r="C9" s="1">
-        <v>3000</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>508</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>509</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1000</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/targets.xlsx
+++ b/inputs/targets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80DD9F9-E07A-4B29-B444-BA0FBB34F5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325FAC16-E9D2-437D-B592-0F14B2B023AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29775" yWindow="1725" windowWidth="10845" windowHeight="7005" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
+    <workbookView xWindow="29865" yWindow="5820" windowWidth="12555" windowHeight="8415" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="C2" s="1">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -451,10 +451,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="C3" s="1">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -468,10 +468,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>300000</v>
+        <v>900000</v>
       </c>
       <c r="C4" s="1">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>10</v>

--- a/inputs/targets.xlsx
+++ b/inputs/targets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325FAC16-E9D2-437D-B592-0F14B2B023AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9EB8E6-51E7-496A-A57E-6AAFE0537CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29865" yWindow="5820" windowWidth="12555" windowHeight="8415" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
+    <workbookView xWindow="28980" yWindow="420" windowWidth="8955" windowHeight="6840" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,10 +434,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>300000</v>
+        <v>20000</v>
       </c>
       <c r="C2" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -451,10 +451,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>800000</v>
+        <v>25000</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="D3">
         <v>10</v>
@@ -468,10 +468,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>900000</v>
+        <v>30000</v>
       </c>
       <c r="C4" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D4">
         <v>10</v>

--- a/inputs/targets.xlsx
+++ b/inputs/targets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\friedele\Repos\DRFM\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9EB8E6-51E7-496A-A57E-6AAFE0537CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C150D62-ED91-4AC3-8B89-FFDE84E5B549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28980" yWindow="420" windowWidth="8955" windowHeight="6840" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
+    <workbookView xWindow="30660" yWindow="1410" windowWidth="14145" windowHeight="10110" xr2:uid="{1A73DCAC-05F6-44F4-89EC-97D45892D8A4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Target_Idx</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Target_Range_m</t>
+  </si>
+  <si>
+    <t>pw</t>
   </si>
 </sst>
 </file>
@@ -403,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8C7F47-36BB-473A-8C1D-3059C9614FE4}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -412,7 +415,7 @@
     <col min="5" max="5" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -428,8 +431,11 @@
       <c r="E1" t="s">
         <v>2</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -437,7 +443,7 @@
         <v>20000</v>
       </c>
       <c r="C2" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D2">
         <v>10</v>
@@ -445,39 +451,88 @@
       <c r="E2" s="2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C3" s="1">
-        <v>-900</v>
+        <v>900</v>
       </c>
       <c r="D3">
         <v>10</v>
       </c>
-      <c r="E3">
-        <v>1</v>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="C4" s="1">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
-      <c r="E4">
-        <v>1</v>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C5" s="1">
+        <v>700</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
+        <v>20000</v>
+      </c>
+      <c r="C6" s="1">
+        <v>600</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
